--- a/artfynd/S 3896-2024 artfynd.xlsx
+++ b/artfynd/S 3896-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/555267</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,8 +902,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131009244</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3896-2024 artfynd.xlsx
+++ b/artfynd/S 3896-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,114 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131009244</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136039919</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58819</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kristinehamn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>459232</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6567694</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Visnum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Molly Wikingson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136039919</t>
         </is>
       </c>
     </row>
@@ -912,6 +1020,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3896-2024 artfynd.xlsx
+++ b/artfynd/S 3896-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>136039919</v>
       </c>
       <c r="B4" t="n">
-        <v>58819</v>
+        <v>58820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3896-2024 artfynd.xlsx
+++ b/artfynd/S 3896-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>136039919</v>
       </c>
       <c r="B4" t="n">
-        <v>58820</v>
+        <v>58824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3896-2024 artfynd.xlsx
+++ b/artfynd/S 3896-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>136039919</v>
       </c>
       <c r="B4" t="n">
-        <v>58824</v>
+        <v>58825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3896-2024 artfynd.xlsx
+++ b/artfynd/S 3896-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>136039919</v>
       </c>
       <c r="B4" t="n">
-        <v>58825</v>
+        <v>58830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 3896-2024 artfynd.xlsx
+++ b/artfynd/S 3896-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>136039919</v>
       </c>
       <c r="B4" t="n">
-        <v>58830</v>
+        <v>58843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
